--- a/New_Outputs/Stats_Exposure_vs_Outcomes.xlsx
+++ b/New_Outputs/Stats_Exposure_vs_Outcomes.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="253" uniqueCount="87">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="278" uniqueCount="91">
   <si>
     <t>predictor</t>
   </si>
@@ -72,6 +72,9 @@
     <t>logROE</t>
   </si>
   <si>
+    <t>family</t>
+  </si>
+  <si>
     <t>test</t>
   </si>
   <si>
@@ -87,10 +90,19 @@
     <t>p_FDR</t>
   </si>
   <si>
+    <t>Exposure difference</t>
+  </si>
+  <si>
     <t>logMME difference (Welch t)</t>
   </si>
   <si>
+    <t>Outcome difference</t>
+  </si>
+  <si>
     <t>NRS difference (Welch t)</t>
+  </si>
+  <si>
+    <t>Slope difference</t>
   </si>
   <si>
     <t>Slope difference (x by Group interaction)</t>
@@ -1173,10 +1185,10 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G25"/>
+  <dimension ref="A1:H25"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
-    <row r="1" spans="1:7" s="1" customFormat="1">
+    <row r="1" spans="1:8" s="1" customFormat="1">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1198,8 +1210,11 @@
       <c r="G1" s="1" t="s">
         <v>22</v>
       </c>
-    </row>
-    <row r="2" spans="1:7">
+      <c r="H1" s="1" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="2" spans="1:8">
       <c r="A2" t="s">
         <v>10</v>
       </c>
@@ -1207,22 +1222,25 @@
         <v>11</v>
       </c>
       <c r="C2" t="s">
-        <v>23</v>
-      </c>
-      <c r="D2">
+        <v>24</v>
+      </c>
+      <c r="D2" t="s">
+        <v>25</v>
+      </c>
+      <c r="E2">
         <v>1.958693008210665</v>
       </c>
-      <c r="E2">
+      <c r="F2">
         <v>38.35700078517384</v>
-      </c>
-      <c r="F2">
-        <v>0.05744870087069845</v>
       </c>
       <c r="G2">
         <v>0.05744870087069845</v>
       </c>
-    </row>
-    <row r="3" spans="1:7">
+      <c r="H2">
+        <v>0.05744870087069845</v>
+      </c>
+    </row>
+    <row r="3" spans="1:8">
       <c r="A3" t="s">
         <v>10</v>
       </c>
@@ -1230,22 +1248,25 @@
         <v>11</v>
       </c>
       <c r="C3" t="s">
-        <v>24</v>
-      </c>
-      <c r="D3">
+        <v>26</v>
+      </c>
+      <c r="D3" t="s">
+        <v>27</v>
+      </c>
+      <c r="E3">
         <v>1.004720731154723</v>
       </c>
-      <c r="E3">
+      <c r="F3">
         <v>37.59871864700813</v>
-      </c>
-      <c r="F3">
-        <v>0.3214539495770256</v>
       </c>
       <c r="G3">
         <v>0.3214539495770256</v>
       </c>
-    </row>
-    <row r="4" spans="1:7">
+      <c r="H3">
+        <v>0.3214539495770256</v>
+      </c>
+    </row>
+    <row r="4" spans="1:8">
       <c r="A4" t="s">
         <v>10</v>
       </c>
@@ -1253,22 +1274,25 @@
         <v>11</v>
       </c>
       <c r="C4" t="s">
-        <v>25</v>
-      </c>
-      <c r="D4">
+        <v>28</v>
+      </c>
+      <c r="D4" t="s">
+        <v>29</v>
+      </c>
+      <c r="E4">
         <v>0.3502388540327029</v>
       </c>
-      <c r="E4">
+      <c r="F4">
         <v>1</v>
       </c>
-      <c r="F4">
+      <c r="G4">
         <v>0.5573932974649053</v>
       </c>
-      <c r="G4">
-        <v>0.9151954684538258</v>
-      </c>
-    </row>
-    <row r="5" spans="1:7">
+      <c r="H4">
+        <v>0.5573932974649053</v>
+      </c>
+    </row>
+    <row r="5" spans="1:8">
       <c r="A5" t="s">
         <v>10</v>
       </c>
@@ -1276,22 +1300,25 @@
         <v>14</v>
       </c>
       <c r="C5" t="s">
-        <v>23</v>
-      </c>
-      <c r="D5">
+        <v>24</v>
+      </c>
+      <c r="D5" t="s">
+        <v>25</v>
+      </c>
+      <c r="E5">
         <v>1.958693008210665</v>
       </c>
-      <c r="E5">
+      <c r="F5">
         <v>38.35700078517384</v>
-      </c>
-      <c r="F5">
-        <v>0.05744870087069845</v>
       </c>
       <c r="G5">
         <v>0.05744870087069845</v>
       </c>
-    </row>
-    <row r="6" spans="1:7">
+      <c r="H5">
+        <v>0.05744870087069845</v>
+      </c>
+    </row>
+    <row r="6" spans="1:8">
       <c r="A6" t="s">
         <v>10</v>
       </c>
@@ -1301,20 +1328,23 @@
       <c r="C6" t="s">
         <v>26</v>
       </c>
-      <c r="D6">
+      <c r="D6" t="s">
+        <v>30</v>
+      </c>
+      <c r="E6">
         <v>1.0333382260487</v>
       </c>
-      <c r="E6">
+      <c r="F6">
         <v>35.03312409380717</v>
-      </c>
-      <c r="F6">
-        <v>0.3085266290026116</v>
       </c>
       <c r="G6">
         <v>0.3085266290026116</v>
       </c>
-    </row>
-    <row r="7" spans="1:7">
+      <c r="H6">
+        <v>0.3085266290026116</v>
+      </c>
+    </row>
+    <row r="7" spans="1:8">
       <c r="A7" t="s">
         <v>10</v>
       </c>
@@ -1322,22 +1352,25 @@
         <v>14</v>
       </c>
       <c r="C7" t="s">
-        <v>25</v>
-      </c>
-      <c r="D7">
+        <v>28</v>
+      </c>
+      <c r="D7" t="s">
+        <v>29</v>
+      </c>
+      <c r="E7">
         <v>0.1907096635552593</v>
       </c>
-      <c r="E7">
+      <c r="F7">
         <v>1</v>
       </c>
-      <c r="F7">
+      <c r="G7">
         <v>0.6647349941207565</v>
       </c>
-      <c r="G7">
-        <v>0.9151954684538258</v>
-      </c>
-    </row>
-    <row r="8" spans="1:7">
+      <c r="H7">
+        <v>0.6647349941207565</v>
+      </c>
+    </row>
+    <row r="8" spans="1:8">
       <c r="A8" t="s">
         <v>10</v>
       </c>
@@ -1345,22 +1378,25 @@
         <v>15</v>
       </c>
       <c r="C8" t="s">
-        <v>23</v>
-      </c>
-      <c r="D8">
+        <v>24</v>
+      </c>
+      <c r="D8" t="s">
+        <v>25</v>
+      </c>
+      <c r="E8">
         <v>1.958693008210665</v>
       </c>
-      <c r="E8">
+      <c r="F8">
         <v>38.35700078517384</v>
-      </c>
-      <c r="F8">
-        <v>0.05744870087069845</v>
       </c>
       <c r="G8">
         <v>0.05744870087069845</v>
       </c>
-    </row>
-    <row r="9" spans="1:7">
+      <c r="H8">
+        <v>0.05744870087069845</v>
+      </c>
+    </row>
+    <row r="9" spans="1:8">
       <c r="A9" t="s">
         <v>10</v>
       </c>
@@ -1368,22 +1404,25 @@
         <v>15</v>
       </c>
       <c r="C9" t="s">
-        <v>27</v>
-      </c>
-      <c r="D9">
+        <v>26</v>
+      </c>
+      <c r="D9" t="s">
+        <v>31</v>
+      </c>
+      <c r="E9">
         <v>1.203617708171545</v>
       </c>
-      <c r="E9">
+      <c r="F9">
         <v>35.80831168230413</v>
-      </c>
-      <c r="F9">
-        <v>0.2366342348398097</v>
       </c>
       <c r="G9">
         <v>0.2366342348398097</v>
       </c>
-    </row>
-    <row r="10" spans="1:7">
+      <c r="H9">
+        <v>0.2366342348398097</v>
+      </c>
+    </row>
+    <row r="10" spans="1:8">
       <c r="A10" t="s">
         <v>10</v>
       </c>
@@ -1391,22 +1430,25 @@
         <v>15</v>
       </c>
       <c r="C10" t="s">
-        <v>25</v>
-      </c>
-      <c r="D10">
+        <v>28</v>
+      </c>
+      <c r="D10" t="s">
+        <v>29</v>
+      </c>
+      <c r="E10">
         <v>0.01148760295413144</v>
       </c>
-      <c r="E10">
+      <c r="F10">
         <v>1</v>
-      </c>
-      <c r="F10">
-        <v>0.9151954684538258</v>
       </c>
       <c r="G10">
         <v>0.9151954684538258</v>
       </c>
-    </row>
-    <row r="11" spans="1:7">
+      <c r="H10">
+        <v>0.9151954684538258</v>
+      </c>
+    </row>
+    <row r="11" spans="1:8">
       <c r="A11" t="s">
         <v>10</v>
       </c>
@@ -1414,22 +1456,25 @@
         <v>16</v>
       </c>
       <c r="C11" t="s">
-        <v>23</v>
-      </c>
-      <c r="D11">
+        <v>24</v>
+      </c>
+      <c r="D11" t="s">
+        <v>25</v>
+      </c>
+      <c r="E11">
         <v>1.958693008210665</v>
       </c>
-      <c r="E11">
+      <c r="F11">
         <v>38.35700078517384</v>
-      </c>
-      <c r="F11">
-        <v>0.05744870087069845</v>
       </c>
       <c r="G11">
         <v>0.05744870087069845</v>
       </c>
-    </row>
-    <row r="12" spans="1:7">
+      <c r="H11">
+        <v>0.05744870087069845</v>
+      </c>
+    </row>
+    <row r="12" spans="1:8">
       <c r="A12" t="s">
         <v>10</v>
       </c>
@@ -1437,22 +1482,25 @@
         <v>16</v>
       </c>
       <c r="C12" t="s">
-        <v>28</v>
-      </c>
-      <c r="D12">
+        <v>26</v>
+      </c>
+      <c r="D12" t="s">
+        <v>32</v>
+      </c>
+      <c r="E12">
         <v>0.7523986538883403</v>
       </c>
-      <c r="E12">
+      <c r="F12">
         <v>37.56016123824169</v>
-      </c>
-      <c r="F12">
-        <v>0.4565010410163731</v>
       </c>
       <c r="G12">
         <v>0.4565010410163731</v>
       </c>
-    </row>
-    <row r="13" spans="1:7">
+      <c r="H12">
+        <v>0.4565010410163731</v>
+      </c>
+    </row>
+    <row r="13" spans="1:8">
       <c r="A13" t="s">
         <v>10</v>
       </c>
@@ -1460,22 +1508,25 @@
         <v>16</v>
       </c>
       <c r="C13" t="s">
-        <v>25</v>
-      </c>
-      <c r="D13">
+        <v>28</v>
+      </c>
+      <c r="D13" t="s">
+        <v>29</v>
+      </c>
+      <c r="E13">
         <v>0.07512719516228289</v>
       </c>
-      <c r="E13">
+      <c r="F13">
         <v>1</v>
       </c>
-      <c r="F13">
+      <c r="G13">
         <v>0.7854594216402239</v>
       </c>
-      <c r="G13">
-        <v>0.9151954684538258</v>
-      </c>
-    </row>
-    <row r="14" spans="1:7">
+      <c r="H13">
+        <v>0.7854594216402239</v>
+      </c>
+    </row>
+    <row r="14" spans="1:8">
       <c r="A14" t="s">
         <v>17</v>
       </c>
@@ -1483,22 +1534,25 @@
         <v>11</v>
       </c>
       <c r="C14" t="s">
-        <v>29</v>
-      </c>
-      <c r="D14">
+        <v>24</v>
+      </c>
+      <c r="D14" t="s">
+        <v>33</v>
+      </c>
+      <c r="E14">
         <v>7.490715546261427</v>
       </c>
-      <c r="E14">
+      <c r="F14">
         <v>27.32553700227097</v>
-      </c>
-      <c r="F14">
-        <v>4.318735888299859E-08</v>
       </c>
       <c r="G14">
         <v>4.318735888299859E-08</v>
       </c>
-    </row>
-    <row r="15" spans="1:7">
+      <c r="H14">
+        <v>4.318735888299859E-08</v>
+      </c>
+    </row>
+    <row r="15" spans="1:8">
       <c r="A15" t="s">
         <v>17</v>
       </c>
@@ -1506,22 +1560,25 @@
         <v>11</v>
       </c>
       <c r="C15" t="s">
-        <v>24</v>
-      </c>
-      <c r="D15">
+        <v>26</v>
+      </c>
+      <c r="D15" t="s">
+        <v>27</v>
+      </c>
+      <c r="E15">
         <v>0.7002939047639797</v>
       </c>
-      <c r="E15">
+      <c r="F15">
         <v>32.42835329510068</v>
-      </c>
-      <c r="F15">
-        <v>0.4887379498863125</v>
       </c>
       <c r="G15">
         <v>0.4887379498863125</v>
       </c>
-    </row>
-    <row r="16" spans="1:7">
+      <c r="H15">
+        <v>0.4887379498863125</v>
+      </c>
+    </row>
+    <row r="16" spans="1:8">
       <c r="A16" t="s">
         <v>17</v>
       </c>
@@ -1529,22 +1586,25 @@
         <v>11</v>
       </c>
       <c r="C16" t="s">
-        <v>25</v>
-      </c>
-      <c r="D16">
+        <v>28</v>
+      </c>
+      <c r="D16" t="s">
+        <v>29</v>
+      </c>
+      <c r="E16">
         <v>7.887379457161621</v>
       </c>
-      <c r="E16">
+      <c r="F16">
         <v>1</v>
       </c>
-      <c r="F16">
+      <c r="G16">
         <v>0.008414306901338762</v>
       </c>
-      <c r="G16">
-        <v>0.03365722760535505</v>
-      </c>
-    </row>
-    <row r="17" spans="1:7">
+      <c r="H16">
+        <v>0.008414306901338762</v>
+      </c>
+    </row>
+    <row r="17" spans="1:8">
       <c r="A17" t="s">
         <v>17</v>
       </c>
@@ -1552,22 +1612,25 @@
         <v>14</v>
       </c>
       <c r="C17" t="s">
-        <v>29</v>
-      </c>
-      <c r="D17">
+        <v>24</v>
+      </c>
+      <c r="D17" t="s">
+        <v>33</v>
+      </c>
+      <c r="E17">
         <v>7.490715546261427</v>
       </c>
-      <c r="E17">
+      <c r="F17">
         <v>27.32553700227097</v>
-      </c>
-      <c r="F17">
-        <v>4.318735888299859E-08</v>
       </c>
       <c r="G17">
         <v>4.318735888299859E-08</v>
       </c>
-    </row>
-    <row r="18" spans="1:7">
+      <c r="H17">
+        <v>4.318735888299859E-08</v>
+      </c>
+    </row>
+    <row r="18" spans="1:8">
       <c r="A18" t="s">
         <v>17</v>
       </c>
@@ -1577,20 +1640,23 @@
       <c r="C18" t="s">
         <v>26</v>
       </c>
-      <c r="D18">
+      <c r="D18" t="s">
+        <v>30</v>
+      </c>
+      <c r="E18">
         <v>1.043486240736477</v>
       </c>
-      <c r="E18">
+      <c r="F18">
         <v>32.94682644158765</v>
-      </c>
-      <c r="F18">
-        <v>0.3043195559508931</v>
       </c>
       <c r="G18">
         <v>0.3043195559508931</v>
       </c>
-    </row>
-    <row r="19" spans="1:7">
+      <c r="H18">
+        <v>0.3043195559508931</v>
+      </c>
+    </row>
+    <row r="19" spans="1:8">
       <c r="A19" t="s">
         <v>17</v>
       </c>
@@ -1598,22 +1664,25 @@
         <v>14</v>
       </c>
       <c r="C19" t="s">
-        <v>25</v>
-      </c>
-      <c r="D19">
+        <v>28</v>
+      </c>
+      <c r="D19" t="s">
+        <v>29</v>
+      </c>
+      <c r="E19">
         <v>4.012150157575824</v>
       </c>
-      <c r="E19">
+      <c r="F19">
         <v>1</v>
       </c>
-      <c r="F19">
+      <c r="G19">
         <v>0.05370501071490765</v>
       </c>
-      <c r="G19">
-        <v>0.1074100214298153</v>
-      </c>
-    </row>
-    <row r="20" spans="1:7">
+      <c r="H19">
+        <v>0.05370501071490765</v>
+      </c>
+    </row>
+    <row r="20" spans="1:8">
       <c r="A20" t="s">
         <v>17</v>
       </c>
@@ -1621,22 +1690,25 @@
         <v>15</v>
       </c>
       <c r="C20" t="s">
-        <v>29</v>
-      </c>
-      <c r="D20">
+        <v>24</v>
+      </c>
+      <c r="D20" t="s">
+        <v>33</v>
+      </c>
+      <c r="E20">
         <v>7.490715546261427</v>
       </c>
-      <c r="E20">
+      <c r="F20">
         <v>27.32553700227097</v>
-      </c>
-      <c r="F20">
-        <v>4.318735888299859E-08</v>
       </c>
       <c r="G20">
         <v>4.318735888299859E-08</v>
       </c>
-    </row>
-    <row r="21" spans="1:7">
+      <c r="H20">
+        <v>4.318735888299859E-08</v>
+      </c>
+    </row>
+    <row r="21" spans="1:8">
       <c r="A21" t="s">
         <v>17</v>
       </c>
@@ -1644,22 +1716,25 @@
         <v>15</v>
       </c>
       <c r="C21" t="s">
-        <v>27</v>
-      </c>
-      <c r="D21">
+        <v>26</v>
+      </c>
+      <c r="D21" t="s">
+        <v>31</v>
+      </c>
+      <c r="E21">
         <v>0.7281418930157973</v>
       </c>
-      <c r="E21">
+      <c r="F21">
         <v>29.62575653176216</v>
-      </c>
-      <c r="F21">
-        <v>0.4722431623557864</v>
       </c>
       <c r="G21">
         <v>0.4722431623557864</v>
       </c>
-    </row>
-    <row r="22" spans="1:7">
+      <c r="H21">
+        <v>0.4722431623557864</v>
+      </c>
+    </row>
+    <row r="22" spans="1:8">
       <c r="A22" t="s">
         <v>17</v>
       </c>
@@ -1667,22 +1742,25 @@
         <v>15</v>
       </c>
       <c r="C22" t="s">
-        <v>25</v>
-      </c>
-      <c r="D22">
+        <v>28</v>
+      </c>
+      <c r="D22" t="s">
+        <v>29</v>
+      </c>
+      <c r="E22">
         <v>3.048733805928183</v>
       </c>
-      <c r="E22">
+      <c r="F22">
         <v>1</v>
       </c>
-      <c r="F22">
+      <c r="G22">
         <v>0.090395356818154</v>
       </c>
-      <c r="G22">
-        <v>0.1205271424242053</v>
-      </c>
-    </row>
-    <row r="23" spans="1:7">
+      <c r="H22">
+        <v>0.090395356818154</v>
+      </c>
+    </row>
+    <row r="23" spans="1:8">
       <c r="A23" t="s">
         <v>17</v>
       </c>
@@ -1690,22 +1768,25 @@
         <v>16</v>
       </c>
       <c r="C23" t="s">
-        <v>29</v>
-      </c>
-      <c r="D23">
+        <v>24</v>
+      </c>
+      <c r="D23" t="s">
+        <v>33</v>
+      </c>
+      <c r="E23">
         <v>7.490715546261427</v>
       </c>
-      <c r="E23">
+      <c r="F23">
         <v>27.32553700227097</v>
-      </c>
-      <c r="F23">
-        <v>4.318735888299859E-08</v>
       </c>
       <c r="G23">
         <v>4.318735888299859E-08</v>
       </c>
-    </row>
-    <row r="24" spans="1:7">
+      <c r="H23">
+        <v>4.318735888299859E-08</v>
+      </c>
+    </row>
+    <row r="24" spans="1:8">
       <c r="A24" t="s">
         <v>17</v>
       </c>
@@ -1713,22 +1794,25 @@
         <v>16</v>
       </c>
       <c r="C24" t="s">
-        <v>28</v>
-      </c>
-      <c r="D24">
+        <v>26</v>
+      </c>
+      <c r="D24" t="s">
+        <v>32</v>
+      </c>
+      <c r="E24">
         <v>0.3252024988979053</v>
       </c>
-      <c r="E24">
+      <c r="F24">
         <v>33.65211873110868</v>
-      </c>
-      <c r="F24">
-        <v>0.7470411044252461</v>
       </c>
       <c r="G24">
         <v>0.7470411044252461</v>
       </c>
-    </row>
-    <row r="25" spans="1:7">
+      <c r="H24">
+        <v>0.7470411044252461</v>
+      </c>
+    </row>
+    <row r="25" spans="1:8">
       <c r="A25" t="s">
         <v>17</v>
       </c>
@@ -1736,18 +1820,21 @@
         <v>16</v>
       </c>
       <c r="C25" t="s">
-        <v>25</v>
-      </c>
-      <c r="D25">
+        <v>28</v>
+      </c>
+      <c r="D25" t="s">
+        <v>29</v>
+      </c>
+      <c r="E25">
         <v>0.007024675100973369</v>
       </c>
-      <c r="E25">
+      <c r="F25">
         <v>1</v>
       </c>
-      <c r="F25">
+      <c r="G25">
         <v>0.9337269826756927</v>
       </c>
-      <c r="G25">
+      <c r="H25">
         <v>0.9337269826756927</v>
       </c>
     </row>
@@ -1763,25 +1850,25 @@
   <sheetData>
     <row r="1" spans="1:12" s="1" customFormat="1">
       <c r="A1" s="1" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="B1" s="1" t="s">
         <v>2</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>31</v>
+        <v>35</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>32</v>
+        <v>36</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>33</v>
+        <v>37</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>35</v>
+        <v>39</v>
       </c>
       <c r="H1" s="1" t="s">
         <v>14</v>
@@ -1793,15 +1880,15 @@
         <v>16</v>
       </c>
       <c r="K1" s="1" t="s">
-        <v>36</v>
+        <v>40</v>
       </c>
       <c r="L1" s="1" t="s">
-        <v>37</v>
+        <v>41</v>
       </c>
     </row>
     <row r="2" spans="1:12">
       <c r="A2" t="s">
-        <v>38</v>
+        <v>42</v>
       </c>
       <c r="B2" t="s">
         <v>12</v>
@@ -1839,7 +1926,7 @@
     </row>
     <row r="3" spans="1:12">
       <c r="A3" t="s">
-        <v>39</v>
+        <v>43</v>
       </c>
       <c r="B3" t="s">
         <v>12</v>
@@ -1877,7 +1964,7 @@
     </row>
     <row r="4" spans="1:12">
       <c r="A4" t="s">
-        <v>40</v>
+        <v>44</v>
       </c>
       <c r="B4" t="s">
         <v>12</v>
@@ -1915,7 +2002,7 @@
     </row>
     <row r="5" spans="1:12">
       <c r="A5" t="s">
-        <v>41</v>
+        <v>45</v>
       </c>
       <c r="B5" t="s">
         <v>13</v>
@@ -1953,7 +2040,7 @@
     </row>
     <row r="6" spans="1:12">
       <c r="A6" t="s">
-        <v>42</v>
+        <v>46</v>
       </c>
       <c r="B6" t="s">
         <v>12</v>
@@ -1968,7 +2055,7 @@
         <v>0</v>
       </c>
       <c r="F6" t="s">
-        <v>43</v>
+        <v>47</v>
       </c>
       <c r="G6">
         <v>6</v>
@@ -1991,7 +2078,7 @@
     </row>
     <row r="7" spans="1:12">
       <c r="A7" t="s">
-        <v>44</v>
+        <v>48</v>
       </c>
       <c r="B7" t="s">
         <v>13</v>
@@ -2029,7 +2116,7 @@
     </row>
     <row r="8" spans="1:12">
       <c r="A8" t="s">
-        <v>45</v>
+        <v>49</v>
       </c>
       <c r="B8" t="s">
         <v>13</v>
@@ -2067,7 +2154,7 @@
     </row>
     <row r="9" spans="1:12">
       <c r="A9" t="s">
-        <v>46</v>
+        <v>50</v>
       </c>
       <c r="B9" t="s">
         <v>12</v>
@@ -2105,7 +2192,7 @@
     </row>
     <row r="10" spans="1:12">
       <c r="A10" t="s">
-        <v>47</v>
+        <v>51</v>
       </c>
       <c r="B10" t="s">
         <v>13</v>
@@ -2143,7 +2230,7 @@
     </row>
     <row r="11" spans="1:12">
       <c r="A11" t="s">
-        <v>48</v>
+        <v>52</v>
       </c>
       <c r="B11" t="s">
         <v>12</v>
@@ -2181,7 +2268,7 @@
     </row>
     <row r="12" spans="1:12">
       <c r="A12" t="s">
-        <v>49</v>
+        <v>53</v>
       </c>
       <c r="B12" t="s">
         <v>12</v>
@@ -2219,7 +2306,7 @@
     </row>
     <row r="13" spans="1:12">
       <c r="A13" t="s">
-        <v>50</v>
+        <v>54</v>
       </c>
       <c r="B13" t="s">
         <v>12</v>
@@ -2257,7 +2344,7 @@
     </row>
     <row r="14" spans="1:12">
       <c r="A14" t="s">
-        <v>51</v>
+        <v>55</v>
       </c>
       <c r="B14" t="s">
         <v>13</v>
@@ -2295,7 +2382,7 @@
     </row>
     <row r="15" spans="1:12">
       <c r="A15" t="s">
-        <v>52</v>
+        <v>56</v>
       </c>
       <c r="B15" t="s">
         <v>13</v>
@@ -2333,7 +2420,7 @@
     </row>
     <row r="16" spans="1:12">
       <c r="A16" t="s">
-        <v>53</v>
+        <v>57</v>
       </c>
       <c r="B16" t="s">
         <v>12</v>
@@ -2348,7 +2435,7 @@
         <v>0</v>
       </c>
       <c r="F16" t="s">
-        <v>43</v>
+        <v>47</v>
       </c>
       <c r="G16">
         <v>8</v>
@@ -2371,7 +2458,7 @@
     </row>
     <row r="17" spans="1:12">
       <c r="A17" t="s">
-        <v>54</v>
+        <v>58</v>
       </c>
       <c r="B17" t="s">
         <v>13</v>
@@ -2409,7 +2496,7 @@
     </row>
     <row r="18" spans="1:12">
       <c r="A18" t="s">
-        <v>55</v>
+        <v>59</v>
       </c>
       <c r="B18" t="s">
         <v>12</v>
@@ -2424,7 +2511,7 @@
         <v>0</v>
       </c>
       <c r="F18" t="s">
-        <v>43</v>
+        <v>47</v>
       </c>
       <c r="G18">
         <v>7</v>
@@ -2447,7 +2534,7 @@
     </row>
     <row r="19" spans="1:12">
       <c r="A19" t="s">
-        <v>56</v>
+        <v>60</v>
       </c>
       <c r="B19" t="s">
         <v>12</v>
@@ -2485,7 +2572,7 @@
     </row>
     <row r="20" spans="1:12">
       <c r="A20" t="s">
-        <v>57</v>
+        <v>61</v>
       </c>
       <c r="B20" t="s">
         <v>12</v>
@@ -2523,7 +2610,7 @@
     </row>
     <row r="21" spans="1:12">
       <c r="A21" t="s">
-        <v>58</v>
+        <v>62</v>
       </c>
       <c r="B21" t="s">
         <v>12</v>
@@ -2561,7 +2648,7 @@
     </row>
     <row r="22" spans="1:12">
       <c r="A22" t="s">
-        <v>59</v>
+        <v>63</v>
       </c>
       <c r="B22" t="s">
         <v>13</v>
@@ -2576,7 +2663,7 @@
         <v>0</v>
       </c>
       <c r="F22" t="s">
-        <v>43</v>
+        <v>47</v>
       </c>
       <c r="G22">
         <v>5</v>
@@ -2599,7 +2686,7 @@
     </row>
     <row r="23" spans="1:12">
       <c r="A23" t="s">
-        <v>60</v>
+        <v>64</v>
       </c>
       <c r="B23" t="s">
         <v>12</v>
@@ -2637,7 +2724,7 @@
     </row>
     <row r="24" spans="1:12">
       <c r="A24" t="s">
-        <v>61</v>
+        <v>65</v>
       </c>
       <c r="B24" t="s">
         <v>12</v>
@@ -2669,7 +2756,7 @@
     </row>
     <row r="25" spans="1:12">
       <c r="A25" t="s">
-        <v>62</v>
+        <v>66</v>
       </c>
       <c r="B25" t="s">
         <v>12</v>
@@ -2707,7 +2794,7 @@
     </row>
     <row r="26" spans="1:12">
       <c r="A26" t="s">
-        <v>63</v>
+        <v>67</v>
       </c>
       <c r="B26" t="s">
         <v>12</v>
@@ -2745,7 +2832,7 @@
     </row>
     <row r="27" spans="1:12">
       <c r="A27" t="s">
-        <v>64</v>
+        <v>68</v>
       </c>
       <c r="B27" t="s">
         <v>13</v>
@@ -2783,7 +2870,7 @@
     </row>
     <row r="28" spans="1:12">
       <c r="A28" t="s">
-        <v>65</v>
+        <v>69</v>
       </c>
       <c r="B28" t="s">
         <v>13</v>
@@ -2815,7 +2902,7 @@
     </row>
     <row r="29" spans="1:12">
       <c r="A29" t="s">
-        <v>66</v>
+        <v>70</v>
       </c>
       <c r="B29" t="s">
         <v>13</v>
@@ -2847,7 +2934,7 @@
     </row>
     <row r="30" spans="1:12">
       <c r="A30" t="s">
-        <v>67</v>
+        <v>71</v>
       </c>
       <c r="B30" t="s">
         <v>13</v>
@@ -2879,7 +2966,7 @@
     </row>
     <row r="31" spans="1:12">
       <c r="A31" t="s">
-        <v>68</v>
+        <v>72</v>
       </c>
       <c r="B31" t="s">
         <v>13</v>
@@ -2917,7 +3004,7 @@
     </row>
     <row r="32" spans="1:12">
       <c r="A32" t="s">
-        <v>69</v>
+        <v>73</v>
       </c>
       <c r="B32" t="s">
         <v>12</v>
@@ -2955,7 +3042,7 @@
     </row>
     <row r="33" spans="1:12">
       <c r="A33" t="s">
-        <v>70</v>
+        <v>74</v>
       </c>
       <c r="B33" t="s">
         <v>13</v>
@@ -2993,7 +3080,7 @@
     </row>
     <row r="34" spans="1:12">
       <c r="A34" t="s">
-        <v>71</v>
+        <v>75</v>
       </c>
       <c r="B34" t="s">
         <v>13</v>
@@ -3025,7 +3112,7 @@
     </row>
     <row r="35" spans="1:12">
       <c r="A35" t="s">
-        <v>72</v>
+        <v>76</v>
       </c>
       <c r="B35" t="s">
         <v>12</v>
@@ -3063,7 +3150,7 @@
     </row>
     <row r="36" spans="1:12">
       <c r="A36" t="s">
-        <v>73</v>
+        <v>77</v>
       </c>
       <c r="B36" t="s">
         <v>12</v>
@@ -3078,7 +3165,7 @@
         <v>0</v>
       </c>
       <c r="F36" t="s">
-        <v>43</v>
+        <v>47</v>
       </c>
       <c r="G36">
         <v>3</v>
@@ -3101,7 +3188,7 @@
     </row>
     <row r="37" spans="1:12">
       <c r="A37" t="s">
-        <v>74</v>
+        <v>78</v>
       </c>
       <c r="B37" t="s">
         <v>13</v>
@@ -3139,7 +3226,7 @@
     </row>
     <row r="38" spans="1:12">
       <c r="A38" t="s">
-        <v>75</v>
+        <v>79</v>
       </c>
       <c r="B38" t="s">
         <v>12</v>
@@ -3177,7 +3264,7 @@
     </row>
     <row r="39" spans="1:12">
       <c r="A39" t="s">
-        <v>76</v>
+        <v>80</v>
       </c>
       <c r="B39" t="s">
         <v>13</v>
@@ -3192,7 +3279,7 @@
         <v>0</v>
       </c>
       <c r="F39" t="s">
-        <v>43</v>
+        <v>47</v>
       </c>
       <c r="G39">
         <v>3</v>
@@ -3215,7 +3302,7 @@
     </row>
     <row r="40" spans="1:12">
       <c r="A40" t="s">
-        <v>77</v>
+        <v>81</v>
       </c>
       <c r="B40" t="s">
         <v>12</v>
@@ -3253,7 +3340,7 @@
     </row>
     <row r="41" spans="1:12">
       <c r="A41" t="s">
-        <v>78</v>
+        <v>82</v>
       </c>
       <c r="B41" t="s">
         <v>13</v>
@@ -3291,7 +3378,7 @@
     </row>
     <row r="42" spans="1:12">
       <c r="A42" t="s">
-        <v>79</v>
+        <v>83</v>
       </c>
       <c r="B42" t="s">
         <v>13</v>
@@ -3329,7 +3416,7 @@
     </row>
     <row r="43" spans="1:12">
       <c r="A43" t="s">
-        <v>80</v>
+        <v>84</v>
       </c>
       <c r="B43" t="s">
         <v>13</v>
@@ -3344,7 +3431,7 @@
         <v>0</v>
       </c>
       <c r="F43" t="s">
-        <v>43</v>
+        <v>47</v>
       </c>
       <c r="G43">
         <v>3</v>
@@ -3367,7 +3454,7 @@
     </row>
     <row r="44" spans="1:12">
       <c r="A44" t="s">
-        <v>81</v>
+        <v>85</v>
       </c>
       <c r="B44" t="s">
         <v>13</v>
@@ -3382,7 +3469,7 @@
         <v>0</v>
       </c>
       <c r="F44" t="s">
-        <v>43</v>
+        <v>47</v>
       </c>
       <c r="G44">
         <v>4</v>
@@ -3405,7 +3492,7 @@
     </row>
     <row r="45" spans="1:12">
       <c r="A45" t="s">
-        <v>82</v>
+        <v>86</v>
       </c>
       <c r="B45" t="s">
         <v>12</v>
@@ -3443,7 +3530,7 @@
     </row>
     <row r="46" spans="1:12">
       <c r="A46" t="s">
-        <v>83</v>
+        <v>87</v>
       </c>
       <c r="B46" t="s">
         <v>13</v>
@@ -3475,7 +3562,7 @@
     </row>
     <row r="47" spans="1:12">
       <c r="A47" t="s">
-        <v>84</v>
+        <v>88</v>
       </c>
       <c r="B47" t="s">
         <v>12</v>
@@ -3507,7 +3594,7 @@
     </row>
     <row r="48" spans="1:12">
       <c r="A48" t="s">
-        <v>85</v>
+        <v>89</v>
       </c>
       <c r="B48" t="s">
         <v>13</v>
@@ -3539,7 +3626,7 @@
     </row>
     <row r="49" spans="1:12">
       <c r="A49" t="s">
-        <v>86</v>
+        <v>90</v>
       </c>
       <c r="B49" t="s">
         <v>12</v>

--- a/New_Outputs/Stats_Exposure_vs_Outcomes.xlsx
+++ b/New_Outputs/Stats_Exposure_vs_Outcomes.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="278" uniqueCount="91">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="270" uniqueCount="90">
   <si>
     <t>predictor</t>
   </si>
@@ -157,9 +157,6 @@
   </si>
   <si>
     <t>PRO-028</t>
-  </si>
-  <si>
-    <t>-Inf</t>
   </si>
   <si>
     <t>PRO-039</t>
@@ -933,25 +930,25 @@
         <v>12</v>
       </c>
       <c r="D10">
-        <v>19</v>
+        <v>23</v>
       </c>
       <c r="E10">
-        <v>-2.767530506386757</v>
+        <v>-3.404794466307844</v>
       </c>
       <c r="F10">
         <v>6</v>
       </c>
       <c r="G10">
-        <v>1.582329535361275</v>
+        <v>0.2212353462650801</v>
       </c>
       <c r="H10">
-        <v>10.37914526026911</v>
+        <v>6.753260882715044</v>
       </c>
       <c r="I10">
-        <v>0.4692488926217691</v>
+        <v>0.1621635921380863</v>
       </c>
       <c r="J10">
-        <v>0.04267631785737821</v>
+        <v>0.4597529907634759</v>
       </c>
     </row>
     <row r="11" spans="1:10">
@@ -965,25 +962,25 @@
         <v>13</v>
       </c>
       <c r="D11">
-        <v>17</v>
+        <v>21</v>
       </c>
       <c r="E11">
-        <v>-4.002242932009562</v>
+        <v>-4.46501537847117</v>
       </c>
       <c r="F11">
-        <v>5.470588235294118</v>
+        <v>5.142857142857143</v>
       </c>
       <c r="G11">
-        <v>-3.392455958455038</v>
+        <v>0.3814771143253933</v>
       </c>
       <c r="H11">
-        <v>-8.106844646586287</v>
+        <v>6.846158324854829</v>
       </c>
       <c r="I11">
-        <v>-0.4593926392259144</v>
+        <v>0.1716548046020155</v>
       </c>
       <c r="J11">
-        <v>0.06357888832011298</v>
+        <v>0.4568746028438275</v>
       </c>
     </row>
     <row r="12" spans="1:10">
@@ -997,25 +994,25 @@
         <v>12</v>
       </c>
       <c r="D12">
-        <v>19</v>
+        <v>23</v>
       </c>
       <c r="E12">
-        <v>-2.767530506386757</v>
+        <v>-3.404794466307844</v>
       </c>
       <c r="F12">
-        <v>0.6030865693792425</v>
+        <v>0.5133271259163052</v>
       </c>
       <c r="G12">
-        <v>0.5316207538493335</v>
+        <v>0.1954871923120657</v>
       </c>
       <c r="H12">
-        <v>2.074363223485598</v>
+        <v>1.178920836534484</v>
       </c>
       <c r="I12">
-        <v>0.4290196908563543</v>
+        <v>0.4009532163888917</v>
       </c>
       <c r="J12">
-        <v>0.0668161921771883</v>
+        <v>0.05794559779994363</v>
       </c>
     </row>
     <row r="13" spans="1:10">
@@ -1029,25 +1026,25 @@
         <v>13</v>
       </c>
       <c r="D13">
-        <v>17</v>
+        <v>21</v>
       </c>
       <c r="E13">
-        <v>-4.002242932009562</v>
+        <v>-4.46501537847117</v>
       </c>
       <c r="F13">
-        <v>0.3200773205915622</v>
+        <v>0.1859880493910868</v>
       </c>
       <c r="G13">
-        <v>-0.8045580197637358</v>
+        <v>0.2025643850500412</v>
       </c>
       <c r="H13">
-        <v>-2.899959327399459</v>
+        <v>1.090441143770077</v>
       </c>
       <c r="I13">
-        <v>-0.3092356625360641</v>
+        <v>0.2443742600826792</v>
       </c>
       <c r="J13">
-        <v>0.2271333520344872</v>
+        <v>0.2857084881849534</v>
       </c>
     </row>
     <row r="14" spans="1:10">
@@ -1061,25 +1058,25 @@
         <v>12</v>
       </c>
       <c r="D14">
-        <v>19</v>
+        <v>23</v>
       </c>
       <c r="E14">
-        <v>-2.767530506386757</v>
+        <v>-3.404794466307844</v>
       </c>
       <c r="F14">
-        <v>0.3557672850344336</v>
+        <v>0.4187530465270466</v>
       </c>
       <c r="G14">
-        <v>0.3038830085658323</v>
+        <v>-0.04253088728055043</v>
       </c>
       <c r="H14">
-        <v>1.196772781612963</v>
+        <v>0.273944116867066</v>
       </c>
       <c r="I14">
-        <v>0.2336781877076818</v>
+        <v>-0.07418615498526808</v>
       </c>
       <c r="J14">
-        <v>0.3356229058949153</v>
+        <v>0.7365636132137305</v>
       </c>
     </row>
     <row r="15" spans="1:10">
@@ -1093,25 +1090,25 @@
         <v>13</v>
       </c>
       <c r="D15">
-        <v>17</v>
+        <v>21</v>
       </c>
       <c r="E15">
-        <v>-4.002242932009562</v>
+        <v>-4.46501537847117</v>
       </c>
       <c r="F15">
-        <v>0.1191254396177785</v>
+        <v>-0.04238547945758799</v>
       </c>
       <c r="G15">
-        <v>-1.116418018384292</v>
+        <v>0.2322514310109308</v>
       </c>
       <c r="H15">
-        <v>-4.349050683628878</v>
+        <v>0.9946207316781542</v>
       </c>
       <c r="I15">
-        <v>-0.3292082355111976</v>
+        <v>0.2239881860743592</v>
       </c>
       <c r="J15">
-        <v>0.1969467035622448</v>
+        <v>0.3290309543782574</v>
       </c>
     </row>
     <row r="16" spans="1:10">
@@ -1125,25 +1122,25 @@
         <v>12</v>
       </c>
       <c r="D16">
-        <v>19</v>
+        <v>23</v>
       </c>
       <c r="E16">
-        <v>-2.767530506386757</v>
+        <v>-3.404794466307844</v>
       </c>
       <c r="F16">
-        <v>0.3220563322808226</v>
+        <v>0.4141804976810523</v>
       </c>
       <c r="G16">
-        <v>-0.5018190972358806</v>
+        <v>-0.1945123568889227</v>
       </c>
       <c r="H16">
-        <v>-1.066743328006939</v>
+        <v>-0.2480940986828481</v>
       </c>
       <c r="I16">
-        <v>-0.265633085661407</v>
+        <v>-0.2596138614805641</v>
       </c>
       <c r="J16">
-        <v>0.2716993312994362</v>
+        <v>0.2315881431185955</v>
       </c>
     </row>
     <row r="17" spans="1:10">
@@ -1157,25 +1154,25 @@
         <v>13</v>
       </c>
       <c r="D17">
-        <v>17</v>
+        <v>21</v>
       </c>
       <c r="E17">
-        <v>-4.002242932009562</v>
+        <v>-4.46501537847117</v>
       </c>
       <c r="F17">
-        <v>0.1931114175128015</v>
+        <v>0.1386175032678729</v>
       </c>
       <c r="G17">
-        <v>-0.5881012420190703</v>
+        <v>0.0615171450071585</v>
       </c>
       <c r="H17">
-        <v>-2.160612621664068</v>
+        <v>0.4132925017644766</v>
       </c>
       <c r="I17">
-        <v>-0.1602197321244536</v>
+        <v>0.05393997657423399</v>
       </c>
       <c r="J17">
-        <v>0.5390341180955009</v>
+        <v>0.8163696921882325</v>
       </c>
     </row>
   </sheetData>
@@ -1540,16 +1537,16 @@
         <v>33</v>
       </c>
       <c r="E14">
-        <v>7.490715546261427</v>
+        <v>2.724952442438224</v>
       </c>
       <c r="F14">
-        <v>27.32553700227097</v>
+        <v>38.54421617879996</v>
       </c>
       <c r="G14">
-        <v>4.318735888299859E-08</v>
+        <v>0.009618244701263259</v>
       </c>
       <c r="H14">
-        <v>4.318735888299859E-08</v>
+        <v>0.009618244701263259</v>
       </c>
     </row>
     <row r="15" spans="1:8">
@@ -1566,16 +1563,16 @@
         <v>27</v>
       </c>
       <c r="E15">
-        <v>0.7002939047639797</v>
+        <v>1.301181452350416</v>
       </c>
       <c r="F15">
-        <v>32.42835329510068</v>
+        <v>40.7740811212736</v>
       </c>
       <c r="G15">
-        <v>0.4887379498863125</v>
+        <v>0.2005013251456181</v>
       </c>
       <c r="H15">
-        <v>0.4887379498863125</v>
+        <v>0.2005013251456181</v>
       </c>
     </row>
     <row r="16" spans="1:8">
@@ -1592,16 +1589,16 @@
         <v>29</v>
       </c>
       <c r="E16">
-        <v>7.887379457161621</v>
+        <v>0.07878607168596667</v>
       </c>
       <c r="F16">
         <v>1</v>
       </c>
       <c r="G16">
-        <v>0.008414306901338762</v>
+        <v>0.7803960137703703</v>
       </c>
       <c r="H16">
-        <v>0.008414306901338762</v>
+        <v>0.7803960137703703</v>
       </c>
     </row>
     <row r="17" spans="1:8">
@@ -1618,16 +1615,16 @@
         <v>33</v>
       </c>
       <c r="E17">
-        <v>7.490715546261427</v>
+        <v>2.724952442438224</v>
       </c>
       <c r="F17">
-        <v>27.32553700227097</v>
+        <v>38.54421617879996</v>
       </c>
       <c r="G17">
-        <v>4.318735888299859E-08</v>
+        <v>0.009618244701263259</v>
       </c>
       <c r="H17">
-        <v>4.318735888299859E-08</v>
+        <v>0.009618244701263259</v>
       </c>
     </row>
     <row r="18" spans="1:8">
@@ -1644,16 +1641,16 @@
         <v>30</v>
       </c>
       <c r="E18">
-        <v>1.043486240736477</v>
+        <v>1.356789446328267</v>
       </c>
       <c r="F18">
-        <v>32.94682644158765</v>
+        <v>40.13967882289627</v>
       </c>
       <c r="G18">
-        <v>0.3043195559508931</v>
+        <v>0.1824299237404304</v>
       </c>
       <c r="H18">
-        <v>0.3043195559508931</v>
+        <v>0.1824299237404304</v>
       </c>
     </row>
     <row r="19" spans="1:8">
@@ -1670,16 +1667,16 @@
         <v>29</v>
       </c>
       <c r="E19">
-        <v>4.012150157575824</v>
+        <v>0.001251269833037561</v>
       </c>
       <c r="F19">
         <v>1</v>
       </c>
       <c r="G19">
-        <v>0.05370501071490765</v>
+        <v>0.9719580206434568</v>
       </c>
       <c r="H19">
-        <v>0.05370501071490765</v>
+        <v>0.9719580206434568</v>
       </c>
     </row>
     <row r="20" spans="1:8">
@@ -1696,16 +1693,16 @@
         <v>33</v>
       </c>
       <c r="E20">
-        <v>7.490715546261427</v>
+        <v>2.724952442438224</v>
       </c>
       <c r="F20">
-        <v>27.32553700227097</v>
+        <v>38.54421617879996</v>
       </c>
       <c r="G20">
-        <v>4.318735888299859E-08</v>
+        <v>0.009618244701263259</v>
       </c>
       <c r="H20">
-        <v>4.318735888299859E-08</v>
+        <v>0.009618244701263259</v>
       </c>
     </row>
     <row r="21" spans="1:8">
@@ -1722,16 +1719,16 @@
         <v>31</v>
       </c>
       <c r="E21">
-        <v>0.7281418930157973</v>
+        <v>1.566407073895623</v>
       </c>
       <c r="F21">
-        <v>29.62575653176216</v>
+        <v>39.05123722171633</v>
       </c>
       <c r="G21">
-        <v>0.4722431623557864</v>
+        <v>0.1253218359991396</v>
       </c>
       <c r="H21">
-        <v>0.4722431623557864</v>
+        <v>0.1253218359991396</v>
       </c>
     </row>
     <row r="22" spans="1:8">
@@ -1748,16 +1745,16 @@
         <v>29</v>
       </c>
       <c r="E22">
-        <v>3.048733805928183</v>
+        <v>1.174709195052076</v>
       </c>
       <c r="F22">
         <v>1</v>
       </c>
       <c r="G22">
-        <v>0.090395356818154</v>
+        <v>0.2849256722297105</v>
       </c>
       <c r="H22">
-        <v>0.090395356818154</v>
+        <v>0.2849256722297105</v>
       </c>
     </row>
     <row r="23" spans="1:8">
@@ -1774,16 +1771,16 @@
         <v>33</v>
       </c>
       <c r="E23">
-        <v>7.490715546261427</v>
+        <v>2.724952442438224</v>
       </c>
       <c r="F23">
-        <v>27.32553700227097</v>
+        <v>38.54421617879996</v>
       </c>
       <c r="G23">
-        <v>4.318735888299859E-08</v>
+        <v>0.009618244701263259</v>
       </c>
       <c r="H23">
-        <v>4.318735888299859E-08</v>
+        <v>0.009618244701263259</v>
       </c>
     </row>
     <row r="24" spans="1:8">
@@ -1800,16 +1797,16 @@
         <v>32</v>
       </c>
       <c r="E24">
-        <v>0.3252024988979053</v>
+        <v>0.7904333194173133</v>
       </c>
       <c r="F24">
-        <v>33.65211873110868</v>
+        <v>41.53229187678567</v>
       </c>
       <c r="G24">
-        <v>0.7470411044252461</v>
+        <v>0.433765101511417</v>
       </c>
       <c r="H24">
-        <v>0.7470411044252461</v>
+        <v>0.433765101511417</v>
       </c>
     </row>
     <row r="25" spans="1:8">
@@ -1826,16 +1823,16 @@
         <v>29</v>
       </c>
       <c r="E25">
-        <v>0.007024675100973369</v>
+        <v>0.7197892207842315</v>
       </c>
       <c r="F25">
         <v>1</v>
       </c>
       <c r="G25">
-        <v>0.9337269826756927</v>
+        <v>0.4012617224003404</v>
       </c>
       <c r="H25">
-        <v>0.9337269826756927</v>
+        <v>0.4012617224003404</v>
       </c>
     </row>
   </sheetData>
@@ -2054,8 +2051,8 @@
       <c r="E6">
         <v>0</v>
       </c>
-      <c r="F6" t="s">
-        <v>47</v>
+      <c r="F6">
+        <v>-6.431798275933005</v>
       </c>
       <c r="G6">
         <v>6</v>
@@ -2078,7 +2075,7 @@
     </row>
     <row r="7" spans="1:12">
       <c r="A7" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="B7" t="s">
         <v>13</v>
@@ -2116,7 +2113,7 @@
     </row>
     <row r="8" spans="1:12">
       <c r="A8" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="B8" t="s">
         <v>13</v>
@@ -2154,7 +2151,7 @@
     </row>
     <row r="9" spans="1:12">
       <c r="A9" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="B9" t="s">
         <v>12</v>
@@ -2192,7 +2189,7 @@
     </row>
     <row r="10" spans="1:12">
       <c r="A10" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="B10" t="s">
         <v>13</v>
@@ -2230,7 +2227,7 @@
     </row>
     <row r="11" spans="1:12">
       <c r="A11" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="B11" t="s">
         <v>12</v>
@@ -2268,7 +2265,7 @@
     </row>
     <row r="12" spans="1:12">
       <c r="A12" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="B12" t="s">
         <v>12</v>
@@ -2306,7 +2303,7 @@
     </row>
     <row r="13" spans="1:12">
       <c r="A13" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="B13" t="s">
         <v>12</v>
@@ -2344,7 +2341,7 @@
     </row>
     <row r="14" spans="1:12">
       <c r="A14" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="B14" t="s">
         <v>13</v>
@@ -2382,7 +2379,7 @@
     </row>
     <row r="15" spans="1:12">
       <c r="A15" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="B15" t="s">
         <v>13</v>
@@ -2420,7 +2417,7 @@
     </row>
     <row r="16" spans="1:12">
       <c r="A16" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="B16" t="s">
         <v>12</v>
@@ -2434,8 +2431,8 @@
       <c r="E16">
         <v>0</v>
       </c>
-      <c r="F16" t="s">
-        <v>47</v>
+      <c r="F16">
+        <v>-6.431798275933005</v>
       </c>
       <c r="G16">
         <v>8</v>
@@ -2458,7 +2455,7 @@
     </row>
     <row r="17" spans="1:12">
       <c r="A17" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="B17" t="s">
         <v>13</v>
@@ -2496,7 +2493,7 @@
     </row>
     <row r="18" spans="1:12">
       <c r="A18" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="B18" t="s">
         <v>12</v>
@@ -2510,8 +2507,8 @@
       <c r="E18">
         <v>0</v>
       </c>
-      <c r="F18" t="s">
-        <v>47</v>
+      <c r="F18">
+        <v>-6.431798275933005</v>
       </c>
       <c r="G18">
         <v>7</v>
@@ -2534,7 +2531,7 @@
     </row>
     <row r="19" spans="1:12">
       <c r="A19" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="B19" t="s">
         <v>12</v>
@@ -2572,7 +2569,7 @@
     </row>
     <row r="20" spans="1:12">
       <c r="A20" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="B20" t="s">
         <v>12</v>
@@ -2610,7 +2607,7 @@
     </row>
     <row r="21" spans="1:12">
       <c r="A21" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="B21" t="s">
         <v>12</v>
@@ -2648,7 +2645,7 @@
     </row>
     <row r="22" spans="1:12">
       <c r="A22" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="B22" t="s">
         <v>13</v>
@@ -2662,8 +2659,8 @@
       <c r="E22">
         <v>0</v>
       </c>
-      <c r="F22" t="s">
-        <v>47</v>
+      <c r="F22">
+        <v>-6.431798275933005</v>
       </c>
       <c r="G22">
         <v>5</v>
@@ -2686,7 +2683,7 @@
     </row>
     <row r="23" spans="1:12">
       <c r="A23" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="B23" t="s">
         <v>12</v>
@@ -2724,7 +2721,7 @@
     </row>
     <row r="24" spans="1:12">
       <c r="A24" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="B24" t="s">
         <v>12</v>
@@ -2756,7 +2753,7 @@
     </row>
     <row r="25" spans="1:12">
       <c r="A25" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="B25" t="s">
         <v>12</v>
@@ -2794,7 +2791,7 @@
     </row>
     <row r="26" spans="1:12">
       <c r="A26" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="B26" t="s">
         <v>12</v>
@@ -2832,7 +2829,7 @@
     </row>
     <row r="27" spans="1:12">
       <c r="A27" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="B27" t="s">
         <v>13</v>
@@ -2870,7 +2867,7 @@
     </row>
     <row r="28" spans="1:12">
       <c r="A28" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="B28" t="s">
         <v>13</v>
@@ -2902,7 +2899,7 @@
     </row>
     <row r="29" spans="1:12">
       <c r="A29" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="B29" t="s">
         <v>13</v>
@@ -2934,7 +2931,7 @@
     </row>
     <row r="30" spans="1:12">
       <c r="A30" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="B30" t="s">
         <v>13</v>
@@ -2966,7 +2963,7 @@
     </row>
     <row r="31" spans="1:12">
       <c r="A31" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="B31" t="s">
         <v>13</v>
@@ -3004,7 +3001,7 @@
     </row>
     <row r="32" spans="1:12">
       <c r="A32" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="B32" t="s">
         <v>12</v>
@@ -3042,7 +3039,7 @@
     </row>
     <row r="33" spans="1:12">
       <c r="A33" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="B33" t="s">
         <v>13</v>
@@ -3080,7 +3077,7 @@
     </row>
     <row r="34" spans="1:12">
       <c r="A34" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="B34" t="s">
         <v>13</v>
@@ -3112,7 +3109,7 @@
     </row>
     <row r="35" spans="1:12">
       <c r="A35" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="B35" t="s">
         <v>12</v>
@@ -3150,7 +3147,7 @@
     </row>
     <row r="36" spans="1:12">
       <c r="A36" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="B36" t="s">
         <v>12</v>
@@ -3164,8 +3161,8 @@
       <c r="E36">
         <v>0</v>
       </c>
-      <c r="F36" t="s">
-        <v>47</v>
+      <c r="F36">
+        <v>-6.431798275933005</v>
       </c>
       <c r="G36">
         <v>3</v>
@@ -3188,7 +3185,7 @@
     </row>
     <row r="37" spans="1:12">
       <c r="A37" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="B37" t="s">
         <v>13</v>
@@ -3226,7 +3223,7 @@
     </row>
     <row r="38" spans="1:12">
       <c r="A38" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="B38" t="s">
         <v>12</v>
@@ -3264,7 +3261,7 @@
     </row>
     <row r="39" spans="1:12">
       <c r="A39" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="B39" t="s">
         <v>13</v>
@@ -3278,8 +3275,8 @@
       <c r="E39">
         <v>0</v>
       </c>
-      <c r="F39" t="s">
-        <v>47</v>
+      <c r="F39">
+        <v>-6.431798275933005</v>
       </c>
       <c r="G39">
         <v>3</v>
@@ -3302,7 +3299,7 @@
     </row>
     <row r="40" spans="1:12">
       <c r="A40" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="B40" t="s">
         <v>12</v>
@@ -3340,7 +3337,7 @@
     </row>
     <row r="41" spans="1:12">
       <c r="A41" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="B41" t="s">
         <v>13</v>
@@ -3378,7 +3375,7 @@
     </row>
     <row r="42" spans="1:12">
       <c r="A42" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="B42" t="s">
         <v>13</v>
@@ -3416,7 +3413,7 @@
     </row>
     <row r="43" spans="1:12">
       <c r="A43" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="B43" t="s">
         <v>13</v>
@@ -3430,8 +3427,8 @@
       <c r="E43">
         <v>0</v>
       </c>
-      <c r="F43" t="s">
-        <v>47</v>
+      <c r="F43">
+        <v>-6.431798275933005</v>
       </c>
       <c r="G43">
         <v>3</v>
@@ -3454,7 +3451,7 @@
     </row>
     <row r="44" spans="1:12">
       <c r="A44" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="B44" t="s">
         <v>13</v>
@@ -3468,8 +3465,8 @@
       <c r="E44">
         <v>0</v>
       </c>
-      <c r="F44" t="s">
-        <v>47</v>
+      <c r="F44">
+        <v>-6.431798275933005</v>
       </c>
       <c r="G44">
         <v>4</v>
@@ -3492,7 +3489,7 @@
     </row>
     <row r="45" spans="1:12">
       <c r="A45" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="B45" t="s">
         <v>12</v>
@@ -3530,7 +3527,7 @@
     </row>
     <row r="46" spans="1:12">
       <c r="A46" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="B46" t="s">
         <v>13</v>
@@ -3562,7 +3559,7 @@
     </row>
     <row r="47" spans="1:12">
       <c r="A47" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="B47" t="s">
         <v>12</v>
@@ -3594,7 +3591,7 @@
     </row>
     <row r="48" spans="1:12">
       <c r="A48" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="B48" t="s">
         <v>13</v>
@@ -3626,7 +3623,7 @@
     </row>
     <row r="49" spans="1:12">
       <c r="A49" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="B49" t="s">
         <v>12</v>
